--- a/input/Relação dos erros dos códigos.xlsx
+++ b/input/Relação dos erros dos códigos.xlsx
@@ -1,158 +1,169 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus\Compilador-remote\input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
-    <sheet name="Página1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Página1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
-  <si>
-    <t xml:space="preserve">Nome do arquivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo do erro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descrição do erro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lexico01.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Léxico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro léxico do tipo caractere inicial inválido em identificador (_) na linha 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lexico02.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro léxico do tipo caractere não reconhecido (?) na linha 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lexico03.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro léxico do tipo caractere não reconhecido ($) na linha 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lexico04.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro léxico do tipo caractere não reconhecido (#) na linha 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lexico05.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro léxico do tipo caractere inválido em identificador (@) na linha 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sintatico01.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sintático</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador * inesperado após o operador +. O parser esperava um &lt;fator&gt; (variável, número, etc.). Linha 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sintatico02.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palavra-chave 'var' inesperada. A gramática só permite uma &lt;seção_declaração_variáveis&gt;. Linha 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sintatico03.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palavra-chave function inesperada. A regra &lt;bloco_subrot&gt; não permite aninhamento de sub-rotinas. Linha 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sintatico04.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fim de arquivo (EOF) inesperado. O parser esperava o token . para finalizar o programa. Linha 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sintatico05.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token 'end' inesperado. Não deveria haver o ';' no último comando. Linha 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sintatico06.ras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token ')' inesperado. Não deveria ter () em procedure sem parâmetros</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+  <si>
+    <t>Nome do arquivo</t>
+  </si>
+  <si>
+    <t>Tipo do erro</t>
+  </si>
+  <si>
+    <t>Descrição do erro</t>
+  </si>
+  <si>
+    <t>lexico01.ras</t>
+  </si>
+  <si>
+    <t>Léxico</t>
+  </si>
+  <si>
+    <t>Erro léxico do tipo caractere inicial inválido em identificador (_) na linha 5</t>
+  </si>
+  <si>
+    <t>lexico02.ras</t>
+  </si>
+  <si>
+    <t>Erro léxico do tipo caractere não reconhecido (?) na linha 12</t>
+  </si>
+  <si>
+    <t>lexico03.ras</t>
+  </si>
+  <si>
+    <t>Erro léxico do tipo caractere não reconhecido ($) na linha 6</t>
+  </si>
+  <si>
+    <t>lexico04.ras</t>
+  </si>
+  <si>
+    <t>Erro léxico do tipo caractere não reconhecido (#) na linha 10</t>
+  </si>
+  <si>
+    <t>lexico05.ras</t>
+  </si>
+  <si>
+    <t>Erro léxico do tipo caractere inválido em identificador (@) na linha 3</t>
+  </si>
+  <si>
+    <t>sintatico01.ras</t>
+  </si>
+  <si>
+    <t>Sintático</t>
+  </si>
+  <si>
+    <t>Operador * inesperado após o operador +. O parser esperava um &lt;fator&gt; (variável, número, etc.). Linha 6</t>
+  </si>
+  <si>
+    <t>sintatico02.ras</t>
+  </si>
+  <si>
+    <t>Palavra-chave 'var' inesperada. A gramática só permite uma &lt;seção_declaração_variáveis&gt;. Linha 5</t>
+  </si>
+  <si>
+    <t>sintatico03.ras</t>
+  </si>
+  <si>
+    <t>Palavra-chave function inesperada. A regra &lt;bloco_subrot&gt; não permite aninhamento de sub-rotinas. Linha 9</t>
+  </si>
+  <si>
+    <t>sintatico04.ras</t>
+  </si>
+  <si>
+    <t>Fim de arquivo (EOF) inesperado. O parser esperava o token . para finalizar o programa. Linha 7</t>
+  </si>
+  <si>
+    <t>sintatico05.ras</t>
+  </si>
+  <si>
+    <t>Token 'end' inesperado. Não deveria haver o ';' no último comando. Linha 9</t>
+  </si>
+  <si>
+    <t>sintatico06.ras</t>
+  </si>
+  <si>
+    <t>Token ')' inesperado. Não deveria ter () em procedure sem parâmetros</t>
+  </si>
+  <si>
+    <t>semantico04.ras</t>
+  </si>
+  <si>
+    <t>Semântico</t>
+  </si>
+  <si>
+    <t>sintatico07.ras</t>
+  </si>
+  <si>
+    <t>lexico06.ras</t>
+  </si>
+  <si>
+    <t>semantico01.ras</t>
+  </si>
+  <si>
+    <t>semantico02.ras</t>
+  </si>
+  <si>
+    <t>semantico03.ras</t>
+  </si>
+  <si>
+    <t>Erro léxico do tipo caractere não reconhecido (") na linha 3</t>
+  </si>
+  <si>
+    <t>Erro semântico: Não é possível atribuir uma expressão do tipo 'integer' à variável 'ok' do tipo 'boolean'. Linha 7</t>
+  </si>
+  <si>
+    <t>Erro semântico: Variável 'x' não foi declarada. Linha 3</t>
+  </si>
+  <si>
+    <t>Erro semântico: Chamada à procedure 'q' requer 2 argumentos, mas 1 foi fornecido. Linha 7</t>
+  </si>
+  <si>
+    <t>Erro semântico: Tipos incompatíveis na operação de soma. Não é possível somar 'integer' e 'boolean'. Linha 4</t>
+  </si>
+  <si>
+    <t>Palavra-chave 'var' inesperada. O parser esperava o token ';' para finalizar a declaração do programa. Linha 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,7 +175,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -172,70 +183,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -243,116 +218,161 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
+  <tableStyles count="1">
+    <tableStyle name="Página1-style" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_1" displayName="Tabela_1" ref="A1:C12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_1" displayName="Tabela_1" ref="A1:C18">
   <tableColumns count="3">
     <tableColumn id="1" name="Nome do arquivo"/>
     <tableColumn id="2" name="Tipo do erro"/>
     <tableColumn id="3" name="Descrição do erro"/>
   </tableColumns>
+  <tableStyleInfo name="Página1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -360,24 +380,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -390,7 +419,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -400,13 +435,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -414,6 +451,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -421,177 +459,236 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="12.66796875" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="91.78"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="104.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:3" s="2" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="1:3" s="2" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
-    <tablePart r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>